--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF05DB2-1ED6-40CB-A536-8EB09BE923D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67EA7A8-D80F-4AEA-B6BD-FBD35EDFC51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67EA7A8-D80F-4AEA-B6BD-FBD35EDFC51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D043F3-49E7-4D5D-9234-6097430782D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D043F3-49E7-4D5D-9234-6097430782D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309B1715-43AF-412C-A9A2-5C32B97DB688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="741">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -584,6 +584,12 @@
     <t>*[_]Nebo_AUS</t>
   </si>
   <si>
+    <t>p_Dubbo_AUS</t>
+  </si>
+  <si>
+    <t>*[_]Dubbo_AUS</t>
+  </si>
+  <si>
     <t>p_MountPiper_AUS</t>
   </si>
   <si>
@@ -608,12 +614,6 @@
     <t>*[_]Tarong_AUS</t>
   </si>
   <si>
-    <t>p_Blackwall_AUS</t>
-  </si>
-  <si>
-    <t>*[_]Blackwall_AUS</t>
-  </si>
-  <si>
     <t>p_Bouldercombe_AUS</t>
   </si>
   <si>
@@ -644,6 +644,12 @@
     <t>*[_]Para_AUS</t>
   </si>
   <si>
+    <t>p_Brisbane_AUS</t>
+  </si>
+  <si>
+    <t>*[_]Brisbane_AUS</t>
+  </si>
+  <si>
     <t>p_BulliCreek_AUS</t>
   </si>
   <si>
@@ -728,6 +734,12 @@
     <t>*[_]AUS22p9S118p7E_AUS</t>
   </si>
   <si>
+    <t>p_Morawa_AUS</t>
+  </si>
+  <si>
+    <t>*[_]Morawa_AUS</t>
+  </si>
+  <si>
     <t>p_Canberra_AUS</t>
   </si>
   <si>
@@ -762,6 +774,12 @@
   </si>
   <si>
     <t>*[_]Horsham_AUS</t>
+  </si>
+  <si>
+    <t>p_PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>*[_]PortHedland_AUS</t>
   </si>
   <si>
     <t>p_Kalgoorlie_AUS</t>
@@ -2996,7 +3014,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9596CD-0528-4380-8F2D-D99C9A838BA1}">
-  <dimension ref="B9:E298"/>
+  <dimension ref="B9:E301"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -7047,6 +7065,48 @@
         <v>734</v>
       </c>
       <c r="E298" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="299" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B299" t="s">
+        <v>735</v>
+      </c>
+      <c r="C299" t="s">
+        <v>736</v>
+      </c>
+      <c r="D299" t="s">
+        <v>736</v>
+      </c>
+      <c r="E299" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="300" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B300" t="s">
+        <v>737</v>
+      </c>
+      <c r="C300" t="s">
+        <v>738</v>
+      </c>
+      <c r="D300" t="s">
+        <v>738</v>
+      </c>
+      <c r="E300" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="301" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B301" t="s">
+        <v>739</v>
+      </c>
+      <c r="C301" t="s">
+        <v>740</v>
+      </c>
+      <c r="D301" t="s">
+        <v>740</v>
+      </c>
+      <c r="E301" t="s">
         <v>149</v>
       </c>
     </row>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309B1715-43AF-412C-A9A2-5C32B97DB688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9907F1-06A4-47BB-B866-6117936EDE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9907F1-06A4-47BB-B866-6117936EDE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF631169-C051-4B18-9F1D-CF6FDDCF8701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -443,12 +443,6 @@
     <t>EP_GAS-GT*,EP_OIL-GT*,*gas_turbine*,EN*CT*</t>
   </si>
   <si>
-    <t>EP_GAS-ST*,EP_OIL-ST*</t>
-  </si>
-  <si>
-    <t>EP_GAS-IC*,EP_OIL-IC*,*gas_engine*</t>
-  </si>
-  <si>
     <t>EP_COA-ST*,EP_LIG-ST*,*-CFB*,*coal_subcritical*</t>
   </si>
   <si>
@@ -494,9 +488,6 @@
     <t>-*ror*</t>
   </si>
   <si>
-    <t>EP_GAS-CC*,EP_OIL-CC*,*gas_cc*,*gas_comb*</t>
-  </si>
-  <si>
     <t>EP_COA-SC*,EP_COA-USC*,EP_LIG-SC*,EP_LIG-USC*,*critical*</t>
   </si>
   <si>
@@ -2262,6 +2253,15 @@
   </si>
   <si>
     <t>elc_wof_AUS_052</t>
+  </si>
+  <si>
+    <t>EP_GAS-CC*,EP_OIL-CC*,*gas_cc*,*gas_comb*,*ember</t>
+  </si>
+  <si>
+    <t>EP_GAS-ST*,EP_OIL-ST*,*steam*</t>
+  </si>
+  <si>
+    <t>EP_GAS-IC*,EP_OIL-IC*,*gas_engine*,*internal_comb*</t>
   </si>
 </sst>
 </file>
@@ -2767,10 +2767,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
@@ -2816,18 +2816,18 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -3019,4095 +3019,4095 @@
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" t="s">
         <v>145</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>146</v>
-      </c>
-      <c r="D10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E10" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D14" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D16" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C18" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D18" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D19" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D20" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C22" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D22" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E22" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C23" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D23" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E23" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D24" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D25" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E25" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D26" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C27" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D27" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E27" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D28" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E28" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E29" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C30" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D30" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C31" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D31" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E31" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C32" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D32" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E32" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C33" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D33" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E33" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C34" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D34" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E34" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C35" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D35" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E35" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C36" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D36" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C37" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D37" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E37" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C38" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D38" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E38" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C39" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D39" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E39" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C40" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D40" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E40" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C41" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D41" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E41" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C42" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D42" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E42" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C43" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D43" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E43" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E44" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C45" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D45" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E45" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D46" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E46" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C47" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D47" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E47" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C48" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D48" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E48" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C49" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D49" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E49" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C50" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D50" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C51" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D51" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E51" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C52" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D52" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E52" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C53" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D53" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E53" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C54" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D54" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E54" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D55" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E55" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C56" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D56" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E56" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C57" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D57" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E57" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C58" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D58" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C59" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D59" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E59" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C60" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D60" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E60" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C61" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D61" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E61" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C62" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E62" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C63" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E63" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D64" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E64" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C65" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D65" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E65" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C66" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D66" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E66" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C67" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D67" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E67" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C68" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D68" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E68" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C69" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D69" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E69" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C70" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D70" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E70" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C71" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D71" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E71" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C72" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D72" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E72" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C73" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D73" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E73" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C74" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D74" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E74" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C75" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D75" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E75" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C76" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D76" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E76" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C77" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D77" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E77" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C78" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D78" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E78" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C79" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D79" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E79" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C80" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D80" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E80" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C81" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D81" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E81" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C82" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D82" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E82" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C83" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D83" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E83" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C84" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D84" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E84" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C85" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D85" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E85" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C86" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D86" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E86" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C87" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D87" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E87" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C88" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D88" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E88" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C89" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D89" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E89" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C90" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D90" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E90" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C91" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D91" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E91" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C92" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D92" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E92" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C93" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D93" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E93" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C94" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D94" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E94" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C95" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D95" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E95" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C96" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D96" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E96" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C97" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D97" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E97" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C98" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D98" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E98" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C99" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D99" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E99" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C100" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D100" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E100" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C101" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D101" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E101" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C102" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D102" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E102" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C103" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D103" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E103" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C104" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D104" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E104" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D105" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E105" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C106" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D106" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E106" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C107" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D107" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E107" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C108" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D108" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E108" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C109" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D109" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E109" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C110" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E110" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C111" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E111" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C112" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E112" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C113" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D113" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E113" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C114" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E114" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C115" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E115" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C116" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D116" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E116" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C117" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D117" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E117" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B118" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C118" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D118" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E118" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B119" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C119" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D119" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E119" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C120" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D120" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E120" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C121" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D121" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E121" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C122" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D122" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E122" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B123" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C123" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E123" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C124" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E124" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C125" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E125" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B126" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C126" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E126" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B127" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C127" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D127" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E127" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B128" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C128" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D128" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E128" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C129" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E129" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B130" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C130" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D130" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E130" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B131" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C131" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D131" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E131" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B132" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C132" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D132" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E132" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B133" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C133" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D133" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E133" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B134" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C134" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D134" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E134" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C135" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D135" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E135" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B136" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C136" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D136" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E136" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C137" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D137" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E137" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B138" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C138" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D138" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E138" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B139" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C139" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D139" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E139" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B140" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C140" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D140" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E140" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B141" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C141" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D141" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E141" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B142" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C142" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D142" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E142" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B143" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C143" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D143" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E143" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B144" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C144" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D144" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E144" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B145" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C145" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D145" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E145" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B146" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C146" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D146" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E146" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B147" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C147" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D147" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E147" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B148" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C148" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D148" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E148" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B149" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C149" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D149" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E149" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B150" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C150" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D150" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E150" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B151" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C151" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D151" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E151" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B152" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C152" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D152" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E152" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B153" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C153" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D153" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E153" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B154" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C154" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D154" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E154" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B155" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C155" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D155" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E155" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B156" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C156" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D156" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E156" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B157" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C157" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D157" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E157" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B158" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C158" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D158" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E158" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B159" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C159" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D159" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E159" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B160" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C160" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D160" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E160" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B161" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C161" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D161" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E161" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B162" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C162" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D162" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E162" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B163" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C163" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D163" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E163" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B164" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C164" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D164" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E164" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B165" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C165" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D165" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E165" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B166" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C166" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D166" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E166" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B167" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C167" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D167" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E167" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B168" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C168" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D168" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E168" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B169" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C169" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D169" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E169" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="170" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B170" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C170" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D170" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E170" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B171" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C171" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D171" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E171" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B172" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C172" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D172" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E172" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B173" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C173" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D173" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E173" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B174" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C174" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D174" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E174" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B175" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C175" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D175" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E175" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B176" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C176" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D176" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E176" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B177" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C177" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D177" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E177" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B178" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C178" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D178" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E178" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B179" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C179" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D179" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E179" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B180" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C180" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D180" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E180" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B181" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C181" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D181" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E181" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="182" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B182" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C182" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D182" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E182" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="183" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B183" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C183" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D183" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E183" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="184" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B184" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C184" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D184" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E184" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="185" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B185" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C185" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D185" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E185" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="186" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B186" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C186" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D186" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E186" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="187" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B187" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C187" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D187" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E187" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="188" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B188" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C188" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D188" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E188" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="189" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B189" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C189" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D189" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E189" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="190" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B190" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C190" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D190" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E190" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="191" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B191" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C191" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D191" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E191" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="192" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B192" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C192" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D192" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E192" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="193" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B193" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C193" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D193" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E193" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="194" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B194" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C194" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D194" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E194" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="195" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B195" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C195" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D195" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E195" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="196" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B196" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C196" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D196" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E196" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="197" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B197" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C197" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D197" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E197" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="198" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B198" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C198" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D198" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E198" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="199" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B199" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C199" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D199" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E199" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="200" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B200" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C200" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D200" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E200" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="201" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B201" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C201" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D201" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E201" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="202" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B202" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C202" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D202" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E202" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="203" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B203" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C203" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D203" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E203" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="204" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B204" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C204" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D204" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E204" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="205" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B205" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C205" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D205" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E205" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="206" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B206" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C206" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D206" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E206" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="207" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B207" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C207" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D207" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E207" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="208" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B208" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C208" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D208" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E208" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="209" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B209" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C209" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D209" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E209" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="210" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B210" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C210" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D210" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E210" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="211" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B211" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C211" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D211" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E211" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="212" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B212" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C212" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D212" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E212" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="213" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B213" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C213" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D213" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E213" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="214" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B214" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C214" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D214" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E214" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="215" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B215" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C215" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D215" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E215" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="216" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B216" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C216" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D216" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E216" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="217" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B217" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C217" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D217" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E217" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="218" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B218" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C218" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D218" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E218" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="219" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B219" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C219" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D219" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E219" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="220" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B220" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C220" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D220" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E220" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="221" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B221" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C221" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D221" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E221" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="222" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B222" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C222" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D222" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E222" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="223" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B223" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C223" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D223" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E223" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="224" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B224" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C224" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D224" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E224" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="225" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B225" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C225" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D225" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E225" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="226" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B226" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C226" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D226" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E226" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="227" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B227" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C227" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D227" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E227" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="228" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B228" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C228" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D228" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E228" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="229" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B229" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C229" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D229" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E229" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="230" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B230" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C230" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D230" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E230" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="231" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B231" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C231" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D231" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E231" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="232" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B232" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C232" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D232" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E232" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="233" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B233" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C233" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D233" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E233" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="234" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B234" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C234" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D234" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E234" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="235" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B235" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C235" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D235" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E235" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="236" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B236" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C236" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D236" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E236" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="237" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B237" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C237" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D237" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E237" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B238" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C238" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D238" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E238" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="239" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B239" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C239" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D239" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E239" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="240" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B240" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C240" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D240" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E240" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="241" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B241" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C241" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D241" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E241" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="242" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B242" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C242" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D242" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E242" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="243" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B243" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C243" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D243" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E243" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="244" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B244" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C244" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D244" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E244" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="245" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B245" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C245" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D245" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E245" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="246" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B246" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C246" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D246" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E246" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="247" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B247" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C247" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D247" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E247" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="248" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B248" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C248" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D248" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E248" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="249" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B249" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C249" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D249" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E249" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="250" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B250" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C250" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="D250" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E250" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="251" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B251" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C251" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="D251" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="E251" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="252" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B252" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C252" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D252" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E252" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="253" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B253" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C253" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D253" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E253" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="254" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B254" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C254" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D254" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="E254" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="255" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B255" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C255" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D255" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E255" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="256" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B256" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C256" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D256" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E256" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="257" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B257" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C257" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D257" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E257" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="258" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B258" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C258" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D258" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E258" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="259" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B259" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C259" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D259" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E259" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="260" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B260" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C260" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D260" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="E260" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="261" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B261" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C261" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D261" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E261" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="262" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B262" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C262" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D262" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="E262" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="263" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B263" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C263" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D263" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="E263" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="264" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B264" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C264" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D264" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="E264" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="265" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B265" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C265" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D265" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E265" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="266" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B266" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C266" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D266" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E266" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="267" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B267" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C267" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D267" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E267" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="268" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B268" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C268" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D268" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="E268" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="269" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B269" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C269" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D269" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="E269" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="270" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B270" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C270" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D270" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="E270" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="271" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B271" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C271" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D271" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="E271" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="272" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B272" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C272" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D272" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="E272" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="273" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B273" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C273" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D273" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E273" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="274" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B274" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C274" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D274" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E274" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="275" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B275" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C275" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D275" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E275" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="276" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B276" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C276" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D276" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E276" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="277" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B277" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C277" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D277" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E277" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B278" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C278" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D278" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="E278" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B279" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C279" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D279" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="E279" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B280" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C280" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D280" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E280" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="281" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B281" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C281" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D281" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E281" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="282" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B282" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C282" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D282" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="E282" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="283" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B283" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C283" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D283" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E283" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="284" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B284" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C284" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D284" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E284" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="285" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B285" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C285" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D285" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E285" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="286" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B286" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C286" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D286" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="E286" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="287" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B287" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C287" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D287" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E287" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B288" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C288" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D288" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E288" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="289" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B289" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C289" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D289" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E289" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="290" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B290" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C290" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D290" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E290" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="291" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B291" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C291" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D291" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E291" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="292" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B292" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C292" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D292" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="E292" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="293" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B293" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C293" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D293" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E293" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="294" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B294" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C294" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D294" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E294" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="295" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B295" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C295" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D295" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E295" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="296" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B296" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C296" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D296" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="E296" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="297" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B297" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C297" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D297" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E297" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="298" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B298" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C298" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D298" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="E298" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="299" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B299" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C299" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D299" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="E299" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="300" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B300" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C300" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D300" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E300" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="301" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B301" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C301" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D301" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E301" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -7174,10 +7174,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>738</v>
+      </c>
+      <c r="D3" t="s">
         <v>151</v>
-      </c>
-      <c r="D3" t="s">
-        <v>154</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -7197,7 +7197,7 @@
         <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F4" t="s">
         <v>74</v>
@@ -7214,10 +7214,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>739</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F5" t="s">
         <v>77</v>
@@ -7231,7 +7231,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>135</v>
+        <v>740</v>
       </c>
       <c r="F6" t="s">
         <v>79</v>
@@ -7245,10 +7245,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F7" t="s">
         <v>81</v>
@@ -7265,10 +7265,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F8" t="s">
         <v>83</v>
@@ -7299,7 +7299,7 @@
         <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F10" t="s">
         <v>89</v>
@@ -7316,7 +7316,7 @@
         <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F11" t="s">
         <v>92</v>
@@ -7330,7 +7330,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F12" t="s">
         <v>94</v>
@@ -7344,7 +7344,7 @@
         <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F13" t="s">
         <v>97</v>
@@ -7358,7 +7358,7 @@
         <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F14" t="s">
         <v>99</v>
@@ -7372,10 +7372,10 @@
         <v>96</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F15" t="s">
         <v>101</v>
@@ -7389,10 +7389,10 @@
         <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F16" t="s">
         <v>103</v>
@@ -7406,7 +7406,7 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F17" t="s">
         <v>105</v>
@@ -7467,7 +7467,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D22" t="s">
         <v>118</v>
@@ -7513,7 +7513,7 @@
         <v>123</v>
       </c>
       <c r="F24" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G24" t="s">
         <v>124</v>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF631169-C051-4B18-9F1D-CF6FDDCF8701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624DDA12-65EA-46D1-95B8-8FFDBCA0D6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="739">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -509,6 +509,15 @@
     <t>elc,e[_]*</t>
   </si>
   <si>
+    <t>EP_GAS-IC*,EP_OIL-IC*,*gas_engine*,*internal_comb*</t>
+  </si>
+  <si>
+    <t>EP_GAS-CC*,EP_OIL-CC*,*gas_cc*,*gas_comb*,*ember</t>
+  </si>
+  <si>
+    <t>EP_GAS-ST*,EP_OIL-ST*,*steam*</t>
+  </si>
+  <si>
     <t>p_SydneyWest_AUS</t>
   </si>
   <si>
@@ -575,12 +584,6 @@
     <t>*[_]Nebo_AUS</t>
   </si>
   <si>
-    <t>p_Dubbo_AUS</t>
-  </si>
-  <si>
-    <t>*[_]Dubbo_AUS</t>
-  </si>
-  <si>
     <t>p_MountPiper_AUS</t>
   </si>
   <si>
@@ -2253,15 +2256,6 @@
   </si>
   <si>
     <t>elc_wof_AUS_052</t>
-  </si>
-  <si>
-    <t>EP_GAS-CC*,EP_OIL-CC*,*gas_cc*,*gas_comb*,*ember</t>
-  </si>
-  <si>
-    <t>EP_GAS-ST*,EP_OIL-ST*,*steam*</t>
-  </si>
-  <si>
-    <t>EP_GAS-IC*,EP_OIL-IC*,*gas_engine*,*internal_comb*</t>
   </si>
 </sst>
 </file>
@@ -3014,7 +3008,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9596CD-0528-4380-8F2D-D99C9A838BA1}">
-  <dimension ref="B9:E301"/>
+  <dimension ref="B9:E300"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -3038,13 +3032,13 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
         <v>147</v>
@@ -3052,13 +3046,13 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E12" t="s">
         <v>147</v>
@@ -3066,13 +3060,13 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
         <v>147</v>
@@ -3080,13 +3074,13 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E14" t="s">
         <v>147</v>
@@ -3094,13 +3088,13 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C15" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D15" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E15" t="s">
         <v>147</v>
@@ -3108,13 +3102,13 @@
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C16" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D16" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E16" t="s">
         <v>147</v>
@@ -3122,13 +3116,13 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D17" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E17" t="s">
         <v>147</v>
@@ -3136,13 +3130,13 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C18" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D18" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E18" t="s">
         <v>147</v>
@@ -3150,13 +3144,13 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C19" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D19" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E19" t="s">
         <v>147</v>
@@ -3164,13 +3158,13 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D20" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E20" t="s">
         <v>147</v>
@@ -3178,13 +3172,13 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C21" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D21" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E21" t="s">
         <v>147</v>
@@ -3192,13 +3186,13 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D22" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E22" t="s">
         <v>147</v>
@@ -3206,13 +3200,13 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C23" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D23" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E23" t="s">
         <v>147</v>
@@ -3220,13 +3214,13 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C24" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E24" t="s">
         <v>147</v>
@@ -3234,13 +3228,13 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E25" t="s">
         <v>147</v>
@@ -3248,13 +3242,13 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C26" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D26" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E26" t="s">
         <v>147</v>
@@ -3262,13 +3256,13 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D27" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E27" t="s">
         <v>147</v>
@@ -3276,13 +3270,13 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C28" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D28" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E28" t="s">
         <v>147</v>
@@ -3290,13 +3284,13 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C29" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D29" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E29" t="s">
         <v>147</v>
@@ -3304,13 +3298,13 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C30" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D30" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E30" t="s">
         <v>147</v>
@@ -3318,13 +3312,13 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C31" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D31" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E31" t="s">
         <v>147</v>
@@ -3332,13 +3326,13 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C32" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D32" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E32" t="s">
         <v>147</v>
@@ -3346,13 +3340,13 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C33" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D33" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E33" t="s">
         <v>147</v>
@@ -3360,13 +3354,13 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D34" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E34" t="s">
         <v>147</v>
@@ -3374,13 +3368,13 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C35" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D35" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E35" t="s">
         <v>147</v>
@@ -3388,13 +3382,13 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C36" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D36" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E36" t="s">
         <v>147</v>
@@ -3402,13 +3396,13 @@
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C37" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D37" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E37" t="s">
         <v>147</v>
@@ -3416,13 +3410,13 @@
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C38" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D38" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E38" t="s">
         <v>147</v>
@@ -3430,13 +3424,13 @@
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C39" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D39" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -3444,13 +3438,13 @@
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C40" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D40" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E40" t="s">
         <v>147</v>
@@ -3458,13 +3452,13 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C41" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D41" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E41" t="s">
         <v>147</v>
@@ -3472,13 +3466,13 @@
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C42" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D42" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E42" t="s">
         <v>147</v>
@@ -3486,13 +3480,13 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E43" t="s">
         <v>147</v>
@@ -3500,13 +3494,13 @@
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C44" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D44" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E44" t="s">
         <v>147</v>
@@ -3514,13 +3508,13 @@
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D45" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E45" t="s">
         <v>147</v>
@@ -3528,13 +3522,13 @@
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C46" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E46" t="s">
         <v>147</v>
@@ -3542,13 +3536,13 @@
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C47" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D47" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E47" t="s">
         <v>147</v>
@@ -3556,13 +3550,13 @@
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C48" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D48" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E48" t="s">
         <v>147</v>
@@ -3570,13 +3564,13 @@
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D49" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E49" t="s">
         <v>147</v>
@@ -3584,13 +3578,13 @@
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D50" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E50" t="s">
         <v>147</v>
@@ -3598,13 +3592,13 @@
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C51" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D51" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E51" t="s">
         <v>147</v>
@@ -3612,13 +3606,13 @@
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C52" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D52" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E52" t="s">
         <v>147</v>
@@ -3626,13 +3620,13 @@
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C53" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D53" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E53" t="s">
         <v>147</v>
@@ -3640,13 +3634,13 @@
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C54" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D54" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E54" t="s">
         <v>147</v>
@@ -3654,13 +3648,13 @@
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C55" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D55" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E55" t="s">
         <v>147</v>
@@ -3668,13 +3662,13 @@
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C56" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D56" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E56" t="s">
         <v>147</v>
@@ -3682,13 +3676,13 @@
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C57" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D57" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E57" t="s">
         <v>147</v>
@@ -3696,13 +3690,13 @@
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C58" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D58" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E58" t="s">
         <v>147</v>
@@ -3710,13 +3704,13 @@
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C59" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D59" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E59" t="s">
         <v>147</v>
@@ -3724,13 +3718,13 @@
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C60" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D60" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E60" t="s">
         <v>147</v>
@@ -3738,13 +3732,13 @@
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D61" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E61" t="s">
         <v>147</v>
@@ -3752,13 +3746,13 @@
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C62" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D62" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E62" t="s">
         <v>147</v>
@@ -3766,13 +3760,13 @@
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D63" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E63" t="s">
         <v>147</v>
@@ -3780,13 +3774,13 @@
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C64" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E64" t="s">
         <v>147</v>
@@ -3794,13 +3788,13 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C65" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D65" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E65" t="s">
         <v>147</v>
@@ -3808,13 +3802,13 @@
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C66" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D66" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E66" t="s">
         <v>147</v>
@@ -3822,13 +3816,13 @@
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C67" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D67" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E67" t="s">
         <v>147</v>
@@ -3836,13 +3830,13 @@
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C68" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D68" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E68" t="s">
         <v>147</v>
@@ -3850,13 +3844,13 @@
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C69" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D69" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E69" t="s">
         <v>147</v>
@@ -3864,13 +3858,13 @@
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C70" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D70" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E70" t="s">
         <v>147</v>
@@ -3878,13 +3872,13 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C71" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D71" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E71" t="s">
         <v>147</v>
@@ -3892,13 +3886,13 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C72" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D72" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E72" t="s">
         <v>147</v>
@@ -3906,13 +3900,13 @@
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C73" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D73" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E73" t="s">
         <v>147</v>
@@ -3920,13 +3914,13 @@
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C74" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D74" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E74" t="s">
         <v>147</v>
@@ -3934,13 +3928,13 @@
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C75" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D75" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E75" t="s">
         <v>147</v>
@@ -3948,13 +3942,13 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C76" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D76" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E76" t="s">
         <v>147</v>
@@ -3962,13 +3956,13 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C77" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D77" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E77" t="s">
         <v>147</v>
@@ -3976,13 +3970,13 @@
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C78" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D78" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E78" t="s">
         <v>147</v>
@@ -3990,13 +3984,13 @@
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C79" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D79" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E79" t="s">
         <v>147</v>
@@ -4004,13 +3998,13 @@
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C80" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D80" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E80" t="s">
         <v>147</v>
@@ -4018,13 +4012,13 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C81" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D81" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E81" t="s">
         <v>147</v>
@@ -4032,13 +4026,13 @@
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C82" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D82" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E82" t="s">
         <v>147</v>
@@ -4046,13 +4040,13 @@
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C83" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D83" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E83" t="s">
         <v>147</v>
@@ -4060,13 +4054,13 @@
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C84" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D84" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E84" t="s">
         <v>147</v>
@@ -4074,13 +4068,13 @@
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C85" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D85" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E85" t="s">
         <v>147</v>
@@ -4088,13 +4082,13 @@
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C86" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D86" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E86" t="s">
         <v>147</v>
@@ -4102,13 +4096,13 @@
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C87" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D87" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E87" t="s">
         <v>147</v>
@@ -4116,13 +4110,13 @@
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C88" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D88" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E88" t="s">
         <v>147</v>
@@ -4130,13 +4124,13 @@
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C89" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D89" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E89" t="s">
         <v>147</v>
@@ -4144,13 +4138,13 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C90" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D90" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E90" t="s">
         <v>147</v>
@@ -4158,13 +4152,13 @@
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C91" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D91" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E91" t="s">
         <v>147</v>
@@ -4172,13 +4166,13 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C92" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D92" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E92" t="s">
         <v>147</v>
@@ -4186,13 +4180,13 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C93" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D93" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E93" t="s">
         <v>147</v>
@@ -4200,13 +4194,13 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C94" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D94" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E94" t="s">
         <v>147</v>
@@ -4214,13 +4208,13 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C95" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D95" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E95" t="s">
         <v>147</v>
@@ -4228,13 +4222,13 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C96" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D96" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E96" t="s">
         <v>147</v>
@@ -4242,13 +4236,13 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C97" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D97" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E97" t="s">
         <v>147</v>
@@ -4256,13 +4250,13 @@
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C98" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D98" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E98" t="s">
         <v>147</v>
@@ -4270,13 +4264,13 @@
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C99" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D99" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E99" t="s">
         <v>147</v>
@@ -4284,13 +4278,13 @@
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C100" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D100" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E100" t="s">
         <v>147</v>
@@ -4298,13 +4292,13 @@
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C101" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D101" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E101" t="s">
         <v>147</v>
@@ -4312,13 +4306,13 @@
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C102" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D102" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E102" t="s">
         <v>147</v>
@@ -4326,13 +4320,13 @@
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C103" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D103" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E103" t="s">
         <v>147</v>
@@ -4340,13 +4334,13 @@
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C104" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D104" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E104" t="s">
         <v>147</v>
@@ -4354,13 +4348,13 @@
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C105" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D105" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E105" t="s">
         <v>147</v>
@@ -4368,13 +4362,13 @@
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C106" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D106" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E106" t="s">
         <v>147</v>
@@ -4382,13 +4376,13 @@
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C107" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D107" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E107" t="s">
         <v>147</v>
@@ -4396,13 +4390,13 @@
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C108" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D108" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E108" t="s">
         <v>147</v>
@@ -4410,13 +4404,13 @@
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C109" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D109" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E109" t="s">
         <v>147</v>
@@ -4424,13 +4418,13 @@
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C110" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D110" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E110" t="s">
         <v>147</v>
@@ -4438,13 +4432,13 @@
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C111" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D111" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E111" t="s">
         <v>147</v>
@@ -4452,13 +4446,13 @@
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C112" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D112" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E112" t="s">
         <v>147</v>
@@ -4466,13 +4460,13 @@
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C113" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E113" t="s">
         <v>147</v>
@@ -4480,13 +4474,13 @@
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C114" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D114" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E114" t="s">
         <v>147</v>
@@ -4494,13 +4488,13 @@
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C115" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E115" t="s">
         <v>147</v>
@@ -4508,13 +4502,13 @@
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C116" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E116" t="s">
         <v>147</v>
@@ -4522,13 +4516,13 @@
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C117" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E117" t="s">
         <v>147</v>
@@ -4536,13 +4530,13 @@
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B118" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C118" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D118" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E118" t="s">
         <v>147</v>
@@ -4550,13 +4544,13 @@
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B119" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C119" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D119" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E119" t="s">
         <v>147</v>
@@ -4564,13 +4558,13 @@
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C120" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D120" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E120" t="s">
         <v>147</v>
@@ -4578,13 +4572,13 @@
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C121" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D121" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E121" t="s">
         <v>147</v>
@@ -4592,13 +4586,13 @@
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C122" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D122" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E122" t="s">
         <v>147</v>
@@ -4606,13 +4600,13 @@
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B123" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C123" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D123" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E123" t="s">
         <v>147</v>
@@ -4620,13 +4614,13 @@
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C124" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D124" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E124" t="s">
         <v>147</v>
@@ -4634,13 +4628,13 @@
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C125" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D125" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E125" t="s">
         <v>147</v>
@@ -4648,13 +4642,13 @@
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B126" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C126" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E126" t="s">
         <v>147</v>
@@ -4662,13 +4656,13 @@
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B127" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E127" t="s">
         <v>147</v>
@@ -4676,13 +4670,13 @@
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E128" t="s">
         <v>147</v>
@@ -4690,13 +4684,13 @@
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C129" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D129" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E129" t="s">
         <v>147</v>
@@ -4704,13 +4698,13 @@
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B130" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C130" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D130" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E130" t="s">
         <v>147</v>
@@ -4718,13 +4712,13 @@
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B131" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C131" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D131" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E131" t="s">
         <v>147</v>
@@ -4732,13 +4726,13 @@
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B132" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C132" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E132" t="s">
         <v>147</v>
@@ -4746,13 +4740,13 @@
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B133" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C133" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D133" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E133" t="s">
         <v>147</v>
@@ -4760,13 +4754,13 @@
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B134" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C134" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D134" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E134" t="s">
         <v>147</v>
@@ -4774,13 +4768,13 @@
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C135" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D135" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E135" t="s">
         <v>147</v>
@@ -4788,13 +4782,13 @@
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B136" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C136" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D136" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E136" t="s">
         <v>147</v>
@@ -4802,13 +4796,13 @@
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C137" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D137" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E137" t="s">
         <v>147</v>
@@ -4816,13 +4810,13 @@
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B138" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C138" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D138" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E138" t="s">
         <v>147</v>
@@ -4830,13 +4824,13 @@
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B139" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C139" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D139" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E139" t="s">
         <v>147</v>
@@ -4844,13 +4838,13 @@
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B140" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C140" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D140" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E140" t="s">
         <v>147</v>
@@ -4858,13 +4852,13 @@
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B141" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C141" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D141" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E141" t="s">
         <v>147</v>
@@ -4872,13 +4866,13 @@
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B142" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C142" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D142" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E142" t="s">
         <v>147</v>
@@ -4886,13 +4880,13 @@
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B143" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C143" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D143" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E143" t="s">
         <v>147</v>
@@ -4900,13 +4894,13 @@
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B144" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C144" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D144" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E144" t="s">
         <v>147</v>
@@ -4914,13 +4908,13 @@
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B145" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C145" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D145" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E145" t="s">
         <v>147</v>
@@ -4928,13 +4922,13 @@
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B146" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C146" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D146" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E146" t="s">
         <v>147</v>
@@ -4942,13 +4936,13 @@
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B147" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C147" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D147" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E147" t="s">
         <v>147</v>
@@ -4956,13 +4950,13 @@
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B148" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C148" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D148" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E148" t="s">
         <v>147</v>
@@ -4970,13 +4964,13 @@
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B149" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C149" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D149" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E149" t="s">
         <v>147</v>
@@ -4984,13 +4978,13 @@
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B150" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C150" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D150" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E150" t="s">
         <v>147</v>
@@ -4998,13 +4992,13 @@
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B151" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C151" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D151" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E151" t="s">
         <v>147</v>
@@ -5012,13 +5006,13 @@
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B152" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C152" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D152" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E152" t="s">
         <v>147</v>
@@ -5026,13 +5020,13 @@
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B153" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C153" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D153" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E153" t="s">
         <v>147</v>
@@ -5040,13 +5034,13 @@
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B154" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C154" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D154" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E154" t="s">
         <v>147</v>
@@ -5054,13 +5048,13 @@
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B155" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C155" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D155" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E155" t="s">
         <v>147</v>
@@ -5068,13 +5062,13 @@
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B156" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C156" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D156" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E156" t="s">
         <v>147</v>
@@ -5082,13 +5076,13 @@
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B157" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C157" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D157" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E157" t="s">
         <v>147</v>
@@ -5096,13 +5090,13 @@
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B158" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C158" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D158" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E158" t="s">
         <v>147</v>
@@ -5110,13 +5104,13 @@
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B159" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C159" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D159" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E159" t="s">
         <v>147</v>
@@ -5124,13 +5118,13 @@
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B160" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C160" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D160" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E160" t="s">
         <v>147</v>
@@ -5138,13 +5132,13 @@
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B161" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C161" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D161" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E161" t="s">
         <v>147</v>
@@ -5152,13 +5146,13 @@
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B162" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C162" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D162" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E162" t="s">
         <v>147</v>
@@ -5166,13 +5160,13 @@
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B163" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C163" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D163" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E163" t="s">
         <v>147</v>
@@ -5180,13 +5174,13 @@
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B164" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C164" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D164" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E164" t="s">
         <v>147</v>
@@ -5194,13 +5188,13 @@
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B165" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C165" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D165" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E165" t="s">
         <v>147</v>
@@ -5208,13 +5202,13 @@
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B166" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C166" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D166" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E166" t="s">
         <v>147</v>
@@ -5222,13 +5216,13 @@
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B167" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C167" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D167" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E167" t="s">
         <v>147</v>
@@ -5236,13 +5230,13 @@
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B168" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C168" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D168" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E168" t="s">
         <v>147</v>
@@ -5250,13 +5244,13 @@
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B169" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C169" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D169" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E169" t="s">
         <v>147</v>
@@ -5264,13 +5258,13 @@
     </row>
     <row r="170" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B170" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C170" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D170" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E170" t="s">
         <v>147</v>
@@ -5278,13 +5272,13 @@
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B171" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C171" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D171" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E171" t="s">
         <v>147</v>
@@ -5292,13 +5286,13 @@
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B172" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C172" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D172" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E172" t="s">
         <v>147</v>
@@ -5306,13 +5300,13 @@
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B173" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C173" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D173" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E173" t="s">
         <v>147</v>
@@ -5320,13 +5314,13 @@
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B174" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C174" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D174" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E174" t="s">
         <v>147</v>
@@ -5334,13 +5328,13 @@
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B175" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C175" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D175" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E175" t="s">
         <v>147</v>
@@ -5348,13 +5342,13 @@
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B176" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C176" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D176" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E176" t="s">
         <v>147</v>
@@ -5362,13 +5356,13 @@
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B177" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C177" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D177" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E177" t="s">
         <v>147</v>
@@ -5376,13 +5370,13 @@
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B178" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C178" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D178" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E178" t="s">
         <v>147</v>
@@ -5390,13 +5384,13 @@
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B179" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C179" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D179" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E179" t="s">
         <v>147</v>
@@ -5404,13 +5398,13 @@
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B180" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C180" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D180" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E180" t="s">
         <v>147</v>
@@ -5418,13 +5412,13 @@
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B181" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C181" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D181" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E181" t="s">
         <v>147</v>
@@ -5432,13 +5426,13 @@
     </row>
     <row r="182" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B182" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C182" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D182" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E182" t="s">
         <v>147</v>
@@ -5446,13 +5440,13 @@
     </row>
     <row r="183" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B183" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C183" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D183" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E183" t="s">
         <v>147</v>
@@ -5460,13 +5454,13 @@
     </row>
     <row r="184" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B184" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C184" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D184" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E184" t="s">
         <v>147</v>
@@ -5474,13 +5468,13 @@
     </row>
     <row r="185" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B185" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C185" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D185" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E185" t="s">
         <v>147</v>
@@ -5488,13 +5482,13 @@
     </row>
     <row r="186" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B186" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C186" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D186" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E186" t="s">
         <v>147</v>
@@ -5502,13 +5496,13 @@
     </row>
     <row r="187" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B187" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C187" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D187" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E187" t="s">
         <v>147</v>
@@ -5516,13 +5510,13 @@
     </row>
     <row r="188" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B188" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C188" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D188" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E188" t="s">
         <v>147</v>
@@ -5530,13 +5524,13 @@
     </row>
     <row r="189" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B189" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C189" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D189" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E189" t="s">
         <v>147</v>
@@ -5544,13 +5538,13 @@
     </row>
     <row r="190" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B190" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C190" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D190" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E190" t="s">
         <v>147</v>
@@ -5558,13 +5552,13 @@
     </row>
     <row r="191" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B191" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C191" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D191" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E191" t="s">
         <v>147</v>
@@ -5572,13 +5566,13 @@
     </row>
     <row r="192" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B192" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C192" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D192" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E192" t="s">
         <v>147</v>
@@ -5586,13 +5580,13 @@
     </row>
     <row r="193" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B193" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C193" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D193" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E193" t="s">
         <v>147</v>
@@ -5600,13 +5594,13 @@
     </row>
     <row r="194" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B194" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C194" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D194" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E194" t="s">
         <v>147</v>
@@ -5614,13 +5608,13 @@
     </row>
     <row r="195" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B195" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C195" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D195" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E195" t="s">
         <v>147</v>
@@ -5628,13 +5622,13 @@
     </row>
     <row r="196" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B196" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C196" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D196" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E196" t="s">
         <v>147</v>
@@ -5642,13 +5636,13 @@
     </row>
     <row r="197" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B197" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C197" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D197" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E197" t="s">
         <v>147</v>
@@ -5656,13 +5650,13 @@
     </row>
     <row r="198" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B198" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C198" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D198" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E198" t="s">
         <v>147</v>
@@ -5670,13 +5664,13 @@
     </row>
     <row r="199" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B199" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C199" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D199" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E199" t="s">
         <v>147</v>
@@ -5684,13 +5678,13 @@
     </row>
     <row r="200" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B200" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C200" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D200" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E200" t="s">
         <v>147</v>
@@ -5698,13 +5692,13 @@
     </row>
     <row r="201" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B201" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C201" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D201" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E201" t="s">
         <v>147</v>
@@ -5712,13 +5706,13 @@
     </row>
     <row r="202" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B202" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C202" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D202" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E202" t="s">
         <v>147</v>
@@ -5726,13 +5720,13 @@
     </row>
     <row r="203" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B203" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C203" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D203" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E203" t="s">
         <v>147</v>
@@ -5740,13 +5734,13 @@
     </row>
     <row r="204" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B204" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C204" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D204" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E204" t="s">
         <v>147</v>
@@ -5754,13 +5748,13 @@
     </row>
     <row r="205" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B205" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C205" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D205" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E205" t="s">
         <v>147</v>
@@ -5768,13 +5762,13 @@
     </row>
     <row r="206" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B206" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C206" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D206" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E206" t="s">
         <v>147</v>
@@ -5782,13 +5776,13 @@
     </row>
     <row r="207" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B207" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C207" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D207" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E207" t="s">
         <v>147</v>
@@ -5796,13 +5790,13 @@
     </row>
     <row r="208" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B208" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C208" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D208" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E208" t="s">
         <v>147</v>
@@ -5810,13 +5804,13 @@
     </row>
     <row r="209" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B209" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C209" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D209" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E209" t="s">
         <v>147</v>
@@ -5824,13 +5818,13 @@
     </row>
     <row r="210" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B210" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C210" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D210" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E210" t="s">
         <v>147</v>
@@ -5838,13 +5832,13 @@
     </row>
     <row r="211" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B211" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C211" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D211" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E211" t="s">
         <v>147</v>
@@ -5852,13 +5846,13 @@
     </row>
     <row r="212" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B212" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C212" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D212" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E212" t="s">
         <v>147</v>
@@ -5866,13 +5860,13 @@
     </row>
     <row r="213" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B213" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C213" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D213" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E213" t="s">
         <v>147</v>
@@ -5880,13 +5874,13 @@
     </row>
     <row r="214" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B214" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C214" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D214" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E214" t="s">
         <v>147</v>
@@ -5894,13 +5888,13 @@
     </row>
     <row r="215" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B215" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C215" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D215" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E215" t="s">
         <v>147</v>
@@ -5908,13 +5902,13 @@
     </row>
     <row r="216" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B216" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C216" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D216" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E216" t="s">
         <v>147</v>
@@ -5922,13 +5916,13 @@
     </row>
     <row r="217" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B217" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C217" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D217" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E217" t="s">
         <v>147</v>
@@ -5936,13 +5930,13 @@
     </row>
     <row r="218" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B218" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C218" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D218" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E218" t="s">
         <v>147</v>
@@ -5950,13 +5944,13 @@
     </row>
     <row r="219" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B219" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C219" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D219" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E219" t="s">
         <v>147</v>
@@ -5964,13 +5958,13 @@
     </row>
     <row r="220" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B220" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C220" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D220" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E220" t="s">
         <v>147</v>
@@ -5978,13 +5972,13 @@
     </row>
     <row r="221" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B221" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C221" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D221" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E221" t="s">
         <v>147</v>
@@ -5992,13 +5986,13 @@
     </row>
     <row r="222" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B222" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C222" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D222" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E222" t="s">
         <v>147</v>
@@ -6006,13 +6000,13 @@
     </row>
     <row r="223" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B223" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C223" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D223" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E223" t="s">
         <v>147</v>
@@ -6020,13 +6014,13 @@
     </row>
     <row r="224" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B224" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C224" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D224" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E224" t="s">
         <v>147</v>
@@ -6034,13 +6028,13 @@
     </row>
     <row r="225" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B225" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C225" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D225" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E225" t="s">
         <v>147</v>
@@ -6048,13 +6042,13 @@
     </row>
     <row r="226" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B226" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C226" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D226" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E226" t="s">
         <v>147</v>
@@ -6062,13 +6056,13 @@
     </row>
     <row r="227" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B227" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C227" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D227" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E227" t="s">
         <v>147</v>
@@ -6076,13 +6070,13 @@
     </row>
     <row r="228" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B228" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C228" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D228" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E228" t="s">
         <v>147</v>
@@ -6090,13 +6084,13 @@
     </row>
     <row r="229" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B229" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C229" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D229" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E229" t="s">
         <v>147</v>
@@ -6104,13 +6098,13 @@
     </row>
     <row r="230" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B230" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C230" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D230" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E230" t="s">
         <v>147</v>
@@ -6118,13 +6112,13 @@
     </row>
     <row r="231" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B231" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C231" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D231" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E231" t="s">
         <v>147</v>
@@ -6132,13 +6126,13 @@
     </row>
     <row r="232" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B232" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C232" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D232" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E232" t="s">
         <v>147</v>
@@ -6146,13 +6140,13 @@
     </row>
     <row r="233" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B233" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C233" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D233" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E233" t="s">
         <v>147</v>
@@ -6160,13 +6154,13 @@
     </row>
     <row r="234" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B234" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C234" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D234" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E234" t="s">
         <v>147</v>
@@ -6174,13 +6168,13 @@
     </row>
     <row r="235" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B235" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C235" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D235" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E235" t="s">
         <v>147</v>
@@ -6188,13 +6182,13 @@
     </row>
     <row r="236" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B236" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C236" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D236" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E236" t="s">
         <v>147</v>
@@ -6202,13 +6196,13 @@
     </row>
     <row r="237" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B237" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C237" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D237" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E237" t="s">
         <v>147</v>
@@ -6216,13 +6210,13 @@
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B238" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C238" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D238" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E238" t="s">
         <v>147</v>
@@ -6230,13 +6224,13 @@
     </row>
     <row r="239" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B239" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C239" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D239" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E239" t="s">
         <v>147</v>
@@ -6244,13 +6238,13 @@
     </row>
     <row r="240" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B240" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C240" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D240" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E240" t="s">
         <v>147</v>
@@ -6258,13 +6252,13 @@
     </row>
     <row r="241" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B241" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C241" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D241" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="E241" t="s">
         <v>147</v>
@@ -6272,13 +6266,13 @@
     </row>
     <row r="242" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B242" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C242" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D242" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E242" t="s">
         <v>147</v>
@@ -6286,13 +6280,13 @@
     </row>
     <row r="243" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B243" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C243" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D243" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E243" t="s">
         <v>147</v>
@@ -6300,13 +6294,13 @@
     </row>
     <row r="244" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B244" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C244" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D244" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E244" t="s">
         <v>147</v>
@@ -6314,13 +6308,13 @@
     </row>
     <row r="245" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B245" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C245" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D245" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E245" t="s">
         <v>147</v>
@@ -6328,13 +6322,13 @@
     </row>
     <row r="246" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B246" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C246" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D246" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E246" t="s">
         <v>147</v>
@@ -6342,13 +6336,13 @@
     </row>
     <row r="247" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B247" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C247" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D247" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E247" t="s">
         <v>147</v>
@@ -6356,13 +6350,13 @@
     </row>
     <row r="248" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B248" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C248" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D248" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E248" t="s">
         <v>147</v>
@@ -6370,13 +6364,13 @@
     </row>
     <row r="249" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B249" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C249" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D249" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E249" t="s">
         <v>147</v>
@@ -6384,13 +6378,13 @@
     </row>
     <row r="250" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B250" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C250" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D250" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E250" t="s">
         <v>147</v>
@@ -6398,13 +6392,13 @@
     </row>
     <row r="251" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B251" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C251" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D251" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E251" t="s">
         <v>147</v>
@@ -6412,13 +6406,13 @@
     </row>
     <row r="252" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B252" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C252" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D252" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E252" t="s">
         <v>147</v>
@@ -6426,13 +6420,13 @@
     </row>
     <row r="253" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B253" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C253" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D253" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E253" t="s">
         <v>147</v>
@@ -6440,13 +6434,13 @@
     </row>
     <row r="254" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B254" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C254" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D254" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E254" t="s">
         <v>147</v>
@@ -6454,13 +6448,13 @@
     </row>
     <row r="255" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B255" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C255" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D255" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E255" t="s">
         <v>147</v>
@@ -6468,13 +6462,13 @@
     </row>
     <row r="256" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B256" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C256" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D256" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E256" t="s">
         <v>147</v>
@@ -6482,13 +6476,13 @@
     </row>
     <row r="257" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B257" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C257" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D257" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="E257" t="s">
         <v>147</v>
@@ -6496,13 +6490,13 @@
     </row>
     <row r="258" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B258" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C258" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D258" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E258" t="s">
         <v>147</v>
@@ -6510,13 +6504,13 @@
     </row>
     <row r="259" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B259" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C259" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D259" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E259" t="s">
         <v>147</v>
@@ -6524,13 +6518,13 @@
     </row>
     <row r="260" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B260" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C260" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D260" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E260" t="s">
         <v>147</v>
@@ -6538,13 +6532,13 @@
     </row>
     <row r="261" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B261" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C261" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="D261" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E261" t="s">
         <v>147</v>
@@ -6552,13 +6546,13 @@
     </row>
     <row r="262" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B262" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C262" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="D262" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E262" t="s">
         <v>147</v>
@@ -6566,13 +6560,13 @@
     </row>
     <row r="263" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B263" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C263" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="D263" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E263" t="s">
         <v>147</v>
@@ -6580,13 +6574,13 @@
     </row>
     <row r="264" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B264" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C264" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D264" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E264" t="s">
         <v>147</v>
@@ -6594,13 +6588,13 @@
     </row>
     <row r="265" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B265" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C265" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D265" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E265" t="s">
         <v>147</v>
@@ -6608,13 +6602,13 @@
     </row>
     <row r="266" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B266" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C266" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="D266" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E266" t="s">
         <v>147</v>
@@ -6622,13 +6616,13 @@
     </row>
     <row r="267" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B267" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C267" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D267" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E267" t="s">
         <v>147</v>
@@ -6636,13 +6630,13 @@
     </row>
     <row r="268" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B268" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C268" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D268" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="E268" t="s">
         <v>147</v>
@@ -6650,13 +6644,13 @@
     </row>
     <row r="269" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B269" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C269" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D269" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E269" t="s">
         <v>147</v>
@@ -6664,13 +6658,13 @@
     </row>
     <row r="270" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B270" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C270" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="D270" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E270" t="s">
         <v>147</v>
@@ -6678,13 +6672,13 @@
     </row>
     <row r="271" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B271" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C271" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D271" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E271" t="s">
         <v>147</v>
@@ -6692,13 +6686,13 @@
     </row>
     <row r="272" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B272" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C272" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D272" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E272" t="s">
         <v>147</v>
@@ -6706,13 +6700,13 @@
     </row>
     <row r="273" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B273" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C273" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D273" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E273" t="s">
         <v>147</v>
@@ -6720,13 +6714,13 @@
     </row>
     <row r="274" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B274" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C274" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="D274" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E274" t="s">
         <v>147</v>
@@ -6734,13 +6728,13 @@
     </row>
     <row r="275" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B275" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C275" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D275" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E275" t="s">
         <v>147</v>
@@ -6748,13 +6742,13 @@
     </row>
     <row r="276" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B276" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C276" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D276" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E276" t="s">
         <v>147</v>
@@ -6762,13 +6756,13 @@
     </row>
     <row r="277" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B277" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C277" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D277" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E277" t="s">
         <v>147</v>
@@ -6776,13 +6770,13 @@
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B278" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C278" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D278" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E278" t="s">
         <v>147</v>
@@ -6790,13 +6784,13 @@
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B279" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C279" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D279" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="E279" t="s">
         <v>147</v>
@@ -6804,13 +6798,13 @@
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B280" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C280" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="D280" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E280" t="s">
         <v>147</v>
@@ -6818,13 +6812,13 @@
     </row>
     <row r="281" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B281" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C281" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D281" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="E281" t="s">
         <v>147</v>
@@ -6832,13 +6826,13 @@
     </row>
     <row r="282" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B282" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C282" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D282" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E282" t="s">
         <v>147</v>
@@ -6846,13 +6840,13 @@
     </row>
     <row r="283" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B283" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C283" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D283" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="E283" t="s">
         <v>147</v>
@@ -6860,13 +6854,13 @@
     </row>
     <row r="284" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B284" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C284" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D284" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E284" t="s">
         <v>147</v>
@@ -6874,13 +6868,13 @@
     </row>
     <row r="285" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B285" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C285" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D285" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E285" t="s">
         <v>147</v>
@@ -6888,13 +6882,13 @@
     </row>
     <row r="286" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B286" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C286" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D286" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E286" t="s">
         <v>147</v>
@@ -6902,13 +6896,13 @@
     </row>
     <row r="287" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B287" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C287" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D287" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E287" t="s">
         <v>147</v>
@@ -6916,13 +6910,13 @@
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B288" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C288" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D288" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E288" t="s">
         <v>147</v>
@@ -6930,13 +6924,13 @@
     </row>
     <row r="289" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B289" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C289" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D289" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="E289" t="s">
         <v>147</v>
@@ -6944,13 +6938,13 @@
     </row>
     <row r="290" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B290" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C290" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="D290" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="E290" t="s">
         <v>147</v>
@@ -6958,13 +6952,13 @@
     </row>
     <row r="291" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B291" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C291" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D291" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E291" t="s">
         <v>147</v>
@@ -6972,13 +6966,13 @@
     </row>
     <row r="292" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B292" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C292" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D292" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="E292" t="s">
         <v>147</v>
@@ -6986,13 +6980,13 @@
     </row>
     <row r="293" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B293" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C293" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D293" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="E293" t="s">
         <v>147</v>
@@ -7000,13 +6994,13 @@
     </row>
     <row r="294" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B294" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C294" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D294" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E294" t="s">
         <v>147</v>
@@ -7014,13 +7008,13 @@
     </row>
     <row r="295" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B295" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C295" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D295" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E295" t="s">
         <v>147</v>
@@ -7028,13 +7022,13 @@
     </row>
     <row r="296" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B296" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C296" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="D296" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E296" t="s">
         <v>147</v>
@@ -7042,13 +7036,13 @@
     </row>
     <row r="297" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B297" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C297" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D297" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E297" t="s">
         <v>147</v>
@@ -7056,13 +7050,13 @@
     </row>
     <row r="298" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B298" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C298" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="D298" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="E298" t="s">
         <v>147</v>
@@ -7070,13 +7064,13 @@
     </row>
     <row r="299" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B299" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C299" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D299" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E299" t="s">
         <v>147</v>
@@ -7084,29 +7078,15 @@
     </row>
     <row r="300" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B300" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C300" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D300" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E300" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="301" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B301" t="s">
-        <v>736</v>
-      </c>
-      <c r="C301" t="s">
-        <v>737</v>
-      </c>
-      <c r="D301" t="s">
-        <v>737</v>
-      </c>
-      <c r="E301" t="s">
         <v>147</v>
       </c>
     </row>
@@ -7174,7 +7154,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>738</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
         <v>151</v>
@@ -7214,7 +7194,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>739</v>
+        <v>158</v>
       </c>
       <c r="D5" t="s">
         <v>151</v>
@@ -7231,7 +7211,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>740</v>
+        <v>156</v>
       </c>
       <c r="F6" t="s">
         <v>79</v>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624DDA12-65EA-46D1-95B8-8FFDBCA0D6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70A5DF7-7B7D-496F-B61E-8D48367AD02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70A5DF7-7B7D-496F-B61E-8D48367AD02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6176B94-9102-4B50-B283-CF0EA24E582A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6176B94-9102-4B50-B283-CF0EA24E582A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0F34DB-20C0-4CA3-8616-00863318CD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="743">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -662,6 +662,12 @@
     <t>*[_]Murray_AUS</t>
   </si>
   <si>
+    <t>p_OlympicDamWest_AUS</t>
+  </si>
+  <si>
+    <t>*[_]OlympicDamWest_AUS</t>
+  </si>
+  <si>
     <t>p_Chalumbin_AUS</t>
   </si>
   <si>
@@ -774,6 +780,12 @@
   </si>
   <si>
     <t>*[_]PortHedland_AUS</t>
+  </si>
+  <si>
+    <t>p_AUS42p8S146p2E_AUS</t>
+  </si>
+  <si>
+    <t>*[_]AUS42p8S146p2E_AUS</t>
   </si>
   <si>
     <t>p_Kalgoorlie_AUS</t>
@@ -3008,7 +3020,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9596CD-0528-4380-8F2D-D99C9A838BA1}">
-  <dimension ref="B9:E300"/>
+  <dimension ref="B9:E302"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -7087,6 +7099,34 @@
         <v>738</v>
       </c>
       <c r="E300" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="301" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B301" t="s">
+        <v>739</v>
+      </c>
+      <c r="C301" t="s">
+        <v>740</v>
+      </c>
+      <c r="D301" t="s">
+        <v>740</v>
+      </c>
+      <c r="E301" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="302" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B302" t="s">
+        <v>741</v>
+      </c>
+      <c r="C302" t="s">
+        <v>742</v>
+      </c>
+      <c r="D302" t="s">
+        <v>742</v>
+      </c>
+      <c r="E302" t="s">
         <v>147</v>
       </c>
     </row>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0F34DB-20C0-4CA3-8616-00863318CD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B07945-5001-45E6-A5EF-EC1436795F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -782,10 +782,10 @@
     <t>*[_]PortHedland_AUS</t>
   </si>
   <si>
-    <t>p_AUS42p8S146p2E_AUS</t>
-  </si>
-  <si>
-    <t>*[_]AUS42p8S146p2E_AUS</t>
+    <t>p_Hobart_AUS</t>
+  </si>
+  <si>
+    <t>*[_]Hobart_AUS</t>
   </si>
   <si>
     <t>p_Kalgoorlie_AUS</t>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B07945-5001-45E6-A5EF-EC1436795F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682EC152-CEDD-4A8C-BC70-FBBB45BF03B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -608,6 +608,12 @@
     <t>*[_]Tarong_AUS</t>
   </si>
   <si>
+    <t>p_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>*[_]Ipswich_AUS</t>
+  </si>
+  <si>
     <t>p_Bouldercombe_AUS</t>
   </si>
   <si>
@@ -638,12 +644,6 @@
     <t>*[_]Para_AUS</t>
   </si>
   <si>
-    <t>p_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>*[_]Brisbane_AUS</t>
-  </si>
-  <si>
     <t>p_BulliCreek_AUS</t>
   </si>
   <si>
@@ -776,16 +776,16 @@
     <t>*[_]Horsham_AUS</t>
   </si>
   <si>
+    <t>p_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>*[_]Kingston_AUS</t>
+  </si>
+  <si>
     <t>p_PortHedland_AUS</t>
   </si>
   <si>
     <t>*[_]PortHedland_AUS</t>
-  </si>
-  <si>
-    <t>p_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>*[_]Hobart_AUS</t>
   </si>
   <si>
     <t>p_Kalgoorlie_AUS</t>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682EC152-CEDD-4A8C-BC70-FBBB45BF03B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F67222-575E-4D92-A049-33DEC296DA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
+++ b/VerveStacks_AUS_grids_kan50/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F67222-575E-4D92-A049-33DEC296DA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5B9EB5-B0E5-4FFE-94B9-12F7FFDB10D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
